--- a/extenbooks/ES1101.xlsx
+++ b/extenbooks/ES1101.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -957,7 +957,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1101 — Net Transfer Rate (Shaikh &amp; Tonak 1987) — PENDING</t>
+          <t># ES1101 — Net Transfer Rate (Shaikh &amp; Tonak 1987)</t>
         </is>
       </c>
     </row>
@@ -969,87 +969,67 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Chapter**: External study — ST 1987. **Status**: book_period_validated. **Period**: 1952-1989. **Units**: share of EC.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Derived: `(S605 + S606 - S604) / S617` = (B_w + G_w - T_w) / EC. The ST 1987 paper's headline measure: the fraction of total compensation that workers receive back from the state net of taxes. Range 1952-1989: [-0.0653, +0.0207] — i.e., -6.5% to +2.1% of total wage bill. Negative most years, brief positive episodes.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>derived from Ch6 components</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage,' in Robert Cherry et al., eds., *The Imperiled Economy*, Vol. I. URPE.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Compute (B_w + G_w - T_w) / EC using S605, S606, S604, and total compensation</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1101.xlsx
+++ b/extenbooks/ES1101.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–1985</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -946,88 +946,125 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1101-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shaikh &amp; Tonak 1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1101 — Net Transfer Rate (Shaikh &amp; Tonak 1987)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study — ST 1987. **Status**: book_period_validated. **Period**: 1952-1989. **Units**: share of EC.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1101 — Net Transfer Rate (Shaikh &amp; Tonak 1987)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Derived: `(S605 + S606 - S604) / S617` = (B_w + G_w - T_w) / EC. The ST 1987 paper's headline measure: the fraction of total compensation that workers receive back from the state net of taxes. Range 1952-1989: [-0.0653, +0.0207] — i.e., -6.5% to +2.1% of total wage bill. Negative most years, brief positive episodes.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>## Citation</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>**Chapter**: External study — ST 1987. **Status**: book_period_validated. **Period**: 1952-1989. **Units**: share of EC.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage,' in Robert Cherry et al., eds., *The Imperiled Economy*, Vol. I. URPE.</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Derived: `(S605 + S606 - S604) / S617` = (B_w + G_w - T_w) / EC. The ST 1987 paper's headline measure: the fraction of total compensation that workers receive back from the state net of taxes. Range 1952-1989: [-0.0653, +0.0207] — i.e., -6.5% to +2.1% of total wage bill. Negative most years, brief positive episodes.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage,' in Robert Cherry et al., eds., *The Imperiled Economy*, Vol. I. URPE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1044,10 +1081,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1072,237 +1109,298 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Net transfer rate = (Benefits received by workers from the state minus taxes paid by workers to the state) / Apparent wage (employee compensation). Formula: NT/AW = (B - T_w) / EC. When negative, this represents a net tax on workers (workers subsidizing the state); when positive, a net transfer to workers. The series covers 1952-1985 and is Shaikh and Tonak's central measure in the 1987 paper. The rate adjusts for inflation, changes in employment, and other cyclical factors. Benefits include Group I (direct: income support, social security, housing, labor training) and the labor share of Group II (education, health, recreation, energy, natural resources, transportation, postal services). Taxes include Group I (social security contributions from employee compensation) and the labor share of Group II (personal income taxes, motor vehicle licenses, property taxes, other taxes). Group III expenditures (defense, general government) and corporate/indirect taxes are excluded.</t>
+          <t>VERBATIM (Shaikh &amp; Tonak 1987, p.186, Empirical Methodology): "Net Transfer (NT) = Benefits and income received by workers from the state - Taxes paid by workers to the state \n NT = B - T_w \n Where: B = Benefits received by workers; T_w = Taxes paid by workers." This is the formal construction of the ES1101 numerator, sign-reversed from Tonak (1984) net tax. It comes directly from the external paper being replicated.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology pp.186-187; Key Formulas section; Abstract)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology, Definition of Net Transfer, pp.151-160)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primary source: Shaikh and Tonak (1987), Table 2 ('Expenditures Received and Taxes Paid by Labor — Net Transfer, 1952-85', p.192). The table contains 34 annual observations in billions of current dollars: benefits received (column 1), taxes paid (column 2), and net transfer (column 3). The net transfer rate is derived by dividing the net transfer by total employee compensation (apparent wage). Methodology for a single year (1964) is illustrated in Appendix Table 1 (p.191). Underlying data from BEA Survey of Current Business (1981 edition, tables at pp.121, 123, 129, 134, 151, 159, 170) and BLS employment/wage series.</t>
+          <t>VERBATIM (Shaikh &amp; Tonak 1987, p.186): "Because the net transfer is negative over most of this period (1952-1985), it actually represents a net tax on workers." This is the central qualitative claim that ES1101 instantiates over 34 annual observations and is the cross-check for sign conventions when reconciling with ES1002.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192; Appendix Table 1 p.191; Data Sources section)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology, Key Point following NT formula, p.162)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Key benchmarks from Table 2 and Figure 3: 1952 net transfer = -13.57 billion (rate approx -6%); 1966 net transfer = -11.37 billion (benchmark reference year); 1971 net transfer = +9.15 billion (first positive year); 1975 net transfer = +47.42 billion (peak, rate = +5.4%); 1980 net transfer = +11.74 billion; 1985 net transfer = -237.44 billion (rate = -11.0%, all-time low). Phase structure: Phase 1 (1952-1969) range -2% to -7%, stabilizes around -3%; Phase 2 (1969-1975) rises sharply to +5.4%; Phase 3 (1975-1985) falls to -11.0% driven by Reagan-era benefit cuts and rising taxes. Note: 1979 entry in Table 2 printed as '2979' — appears to be a transcription error for 1979.</t>
+          <t>VERBATIM (Shaikh &amp; Tonak 1987, p.190, Phase 3 analysis): "It is striking that by 1985 the social benefit rate is at a level below that of 1966 ... while the tax rate continued to climb to an all time high (41 percent higher than in 1966, in Figure 3). The net transfer rate therefore falls dramatically from +5.4 percent in 1975 to -11.0 percent in 1985 (an all time low)." Provides the two endpoint validation anchors for ES1101 (+5.4% in 1975, -11.0% in 1985) and the 1966 baseline comparison — drawn from the external paper, not ST 1994.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192; Figure 3 description pp.188-189; Three Historical Phases pp.189-190)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Results, Phase 3, Critical Finding for 1985, lines 492-495)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Registry construction formula: (B_w - T_w) / EC, inputs S605, S604, BEA_NIPA. This matches S&amp;T (1987) formula NT/AW = (B - T_w)/EC exactly. S605 carries benefits received by workers; S604 carries taxes paid by workers; BEA_NIPA provides employee compensation (EC/AW) denominator. The 1987 paper is the direct methodological source for the S605/S604 series construction in the ST2 project.</t>
+          <t>Net Transfer (NT) = Benefits and income received by workers from the state - Taxes paid by workers to the state
+NT = B - T_w</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology, Net Transfer Rate formula); series_registry.json#ES1101</t>
+          <t>Shaikh &amp; Tonak 1987, Empirical Methodology, p.186</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 1985 raw net transfer value in Table 2 (-237.44 billion) is anomalously large relative to surrounding years and may reflect a data revision, definitional change, or transcription issue in the source document. The authors' own analysis focuses on the rate (expressed as -11.0% of employee compensation in 1985), which is more robust to level issues. Researchers computing ES1101 should use the rate figures from Figure 3 or the rate formula rather than relying solely on the raw dollar values in Table 2 for the final year.</t>
+          <t>Because the net transfer is negative over most of this period (1952-1985), it actually represents a net tax on workers.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192; Figure 3 description)</t>
+          <t>Shaikh &amp; Tonak 1987, Empirical Methodology, p.186</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The net transfer rate (ES1101) measures the overall impact of state fiscal policy on the standard of living of all workers, including unemployed. It does not represent the impact on the rate of exploitation of productive labor — that requires the narrower Tonak (1984) framework excluding public assistance from benefits (see ES1002). Using ES1101 as a proxy for the exploitation rate adjustment overstates the benefit side because public assistance is included.</t>
+          <t>The net transfer rate therefore falls dramatically from +5.4 percent in 1975 to -11.0 percent in 1985 (an all time low)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 12, p.193-194; Note 14)</t>
+          <t>Shaikh &amp; Tonak 1987, Empirical Results, p.190</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The study covers the United States only, using BEA NIPA data. The labor share allocation method (Group II items allocated proportionally by total labor income / personal income) is an approximation: it assumes workers' share in mixed-income categories scales with their share of personal income. This was critiqued by Miller (1986), who used a tax-shifting approach. S&amp;T (1987) explicitly reject the tax-shifting framework in favor of tracing taxes that flow directly out of employee compensation.</t>
+          <t>Net transfer rate = (Benefits received by workers from the state minus taxes paid by workers to the state) / Apparent wage (employee compensation). Formula: NT/AW = (B - T_w) / EC. When negative, this represents a net tax on workers (workers subsidizing the state); when positive, a net transfer to workers. The series covers 1952-1985 and is Shaikh and Tonak's central measure in the 1987 paper. The rate adjusts for inflation, changes in employment, and other cyclical factors. Benefits include Group I (direct: income support, social security, housing, labor training) and the labor share of Group II (education, health, recreation, energy, natural resources, transportation, postal services). Taxes include Group I (social security contributions from employee compensation) and the labor share of Group II (personal income taxes, motor vehicle licenses, property taxes, other taxes). Group III expenditures (defense, general government) and corporate/indirect taxes are excluded.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 8, pp.193-194; Empirical Methodology)</t>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology pp.186-187; Key Formulas section; Abstract)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEC-012 (No Synthetic Data Policy, 2026-05-03): The ES1101-N1103 series are not listed among the five synthetic-data series requiring remediation, suggesting they were computed from real NIPA inputs via S604/S605. However, if S604 or S605 themselves contain synthetic data, ES1101 inherits that problem. The raw 34-year series is directly available in S&amp;T (1987) Table 2 (p.192) and should be used as the benchmark validation for P19 output.</t>
+          <t>Primary source: Shaikh and Tonak (1987), Table 2 ('Expenditures Received and Taxes Paid by Labor — Net Transfer, 1952-85', p.192). The table contains 34 annual observations in billions of current dollars: benefits received (column 1), taxes paid (column 2), and net transfer (column 3). The net transfer rate is derived by dividing the net transfer by total employee compensation (apparent wage). Methodology for a single year (1964) is illustrated in Appendix Table 1 (p.191). Underlying data from BEA Survey of Current Business (1981 edition, tables at pp.121, 123, 129, 134, 151, 159, 170) and BLS employment/wage series.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-012; 1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192; Appendix Table 1 p.191; Data Sources section)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>empirical_values</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Key benchmarks from Table 2 and Figure 3: 1952 net transfer = -13.57 billion (rate approx -6%); 1966 net transfer = -11.37 billion (benchmark reference year); 1971 net transfer = +9.15 billion (first positive year); 1975 net transfer = +47.42 billion (peak, rate = +5.4%); 1980 net transfer = +11.74 billion; 1985 net transfer = -237.44 billion (rate = -11.0%, all-time low). Phase structure: Phase 1 (1952-1969) range -2% to -7%, stabilizes around -3%; Phase 2 (1969-1975) rises sharply to +5.4%; Phase 3 (1975-1985) falls to -11.0% driven by Reagan-era benefit cuts and rising taxes. Note: 1979 entry in Table 2 printed as '2979' — appears to be a transcription error for 1979.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192; Figure 3 description pp.188-189; Three Historical Phases pp.189-190)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>construction_note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Net transfer rate = (B_w - T_w) / EC, 1952-1985 (34 years). Benefits include direct worker benefits (Group I) plus labor share of social consumption (Group II). Taxes include social security contributions plus labor share of personal taxes. Key finding: negative for 32 of 34 years, meaning workers are net taxpayers; peak +5.4% in 1975 (crisis-induced); all-time low -11.0% in 1985.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Registry construction formula: (B_w - T_w) / EC, inputs S605, S604, BEA_NIPA. This matches S&amp;T (1987) formula NT/AW = (B - T_w)/EC exactly. S605 carries benefits received by workers; S604 carries taxes paid by workers; BEA_NIPA provides employee compensation (EC/AW) denominator. The 1987 paper is the direct methodological source for the S605/S604 series construction in the ST2 project.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Empirical Methodology, Net Transfer Rate formula); series_registry.json#ES1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The 1985 raw net transfer value in Table 2 (-237.44 billion) is anomalously large relative to surrounding years and may reflect a data revision, definitional change, or transcription issue in the source document. The authors' own analysis focuses on the rate (expressed as -11.0% of employee compensation in 1985), which is more robust to level issues. Researchers computing ES1101 should use the rate figures from Figure 3 or the rate formula rather than relying solely on the raw dollar values in Table 2 for the final year.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192; Figure 3 description)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The net transfer rate (ES1101) measures the overall impact of state fiscal policy on the standard of living of all workers, including unemployed. It does not represent the impact on the rate of exploitation of productive labor — that requires the narrower Tonak (1984) framework excluding public assistance from benefits (see ES1002). Using ES1101 as a proxy for the exploitation rate adjustment overstates the benefit side because public assistance is included.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 12, p.193-194; Note 14)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1985 raw dollar value (-237.44B) appears anomalous; use rate figures from Figure 3 for validation</t>
+          <t>The study covers the United States only, using BEA NIPA data. The labor share allocation method (Group II items allocated proportionally by total labor income / personal income) is an approximation: it assumes workers' share in mixed-income categories scales with their share of personal income. This was critiqued by Miller (1986), who used a tax-shifting approach. S&amp;T (1987) explicitly reject the tax-shifting framework in favor of tracing taxes that flow directly out of employee compensation.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Note 8, pp.193-194; Empirical Methodology)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Table 2 contains a likely typo: year listed as '2979' is 1979</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Labor share allocation is an approximation; see Miller (1986) critique</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] (No Synthetic Data Policy, 2026-05-03): The ES1101-N1103 series are not listed among the five synthetic-data series requiring remediation, suggesting they were computed from real NIPA inputs via S604/S605. However, if S604 or S605 themselves contain synthetic data, ES1101 inherits that problem. The raw 34-year series is directly available in S&amp;T (1987) Table 2 (p.192) and should be used as the benchmark validation for P19 output.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]; 1987_Shaikh_Tonak_Social_Wage_Myth/full_transcription.md (Table 2 p.192)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ES1101 includes public assistance in benefits — not appropriate for exploitation rate adjustment (use ES1002 instead)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Net Transfer (NT) = Benefits and income received by workers from the state - Taxes paid by workers to the state
+NT = B - T_w</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+    </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Because the net transfer is negative over most of this period (1952-1985), it actually represents a net tax on workers.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES1001</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ES1002</t>
-        </is>
-      </c>
-    </row>
+          <t>The net transfer rate therefore falls dramatically from +5.4 percent in 1975 to -11.0 percent in 1985 (an all time low)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ES1102</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ES1103</t>
-        </is>
-      </c>
-    </row>
+          <t>Net transfer rate = (B_w - T_w) / EC, 1952-1985 (34 years). Benefits include direct worker benefits (Group I) plus labor share of social consumption (Group II). Taxes include social security contributions plus labor share of personal taxes. Key finding: negative for 32 of 34 years, meaning workers are net taxpayers; peak +5.4% in 1975 (crisis-induced); all-time low -11.0% in 1985.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>S604</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1310,37 +1408,117 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>1985 raw dollar value (-237.44B) appears anomalous; use rate figures from Figure 3 for validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Table 2 contains a likely typo: year listed as '2979' is 1979</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Labor share allocation is an approximation; see Miller (1986) critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES1101 includes public assistance in benefits — not appropriate for exploitation rate adjustment (use ES1002 instead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ES1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ES1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ES1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ES1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>S605</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>ST_1987</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' In Robert Cherry et al. (eds.), The Imperiled Economy, Book I. New York: Union for Radical Political Economics, pp. 184-194.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>BEA_1981</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. 1981. Survey of Current Business. Tables at pp. 121, 123, 129, 134, 151, 159, 170.</t>
         </is>
@@ -1357,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1428,7 +1606,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1627,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1975": 0.054, "1985": -0.11}</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1651,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
